--- a/order_file.xlsx
+++ b/order_file.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>BLOUK EDI Order Form — Bloomsbury Publishing</t>
   </si>
@@ -588,6 +588,15 @@
   </si>
   <si>
     <t>Town/City</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>MLT</t>
+  </si>
+  <si>
+    <t>Malta</t>
   </si>
 </sst>
 </file>
@@ -5266,7 +5275,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid country code" error="Please enter a valid ISO 2-letter code (e.g. GB) or ISO 3-letter alpha-3 code (e.g. GBR)._x000a__x000a_See the Country Codes sheet for the full list of supported codes." promptTitle="Delivery Country" prompt="Enter a 2-letter ISO code (e.g. GB) or 3-letter alpha-3 code (e.g. GBR)." xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>'Country Codes'!$D$2:$D$95</xm:f>
+            <xm:f>'Country Codes'!$D$2:$D$98</xm:f>
           </x14:formula1>
           <xm:sqref>O4:O203</xm:sqref>
         </x14:dataValidation>
@@ -5710,279 +5719,282 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" t="s">
-        <v>87</v>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s" s="3">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s" s="3">
+        <v>189</v>
+      </c>
+      <c r="C31" t="s" s="3">
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D49" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D50" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="13" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -5990,7 +6002,7 @@
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -5998,7 +6010,7 @@
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -6006,211 +6018,229 @@
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D55" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D60" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="D61" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="D62" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D63" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D64" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D65" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D67" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D65" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D66" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D67" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D72" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D73" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D79" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D80" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D81" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D82" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D83" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D84" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D85" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D86" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D87" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D88" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D89" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D90" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D91" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D92" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D93" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D94" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D95" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D97" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D98" t="s">
         <v>182</v>
       </c>
     </row>
